--- a/output/ValueSet-mh-toc-disseminated-intravascular-coagulation-ICD.xlsx
+++ b/output/ValueSet-mh-toc-disseminated-intravascular-coagulation-ICD.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/isseminated-intravascular-coagulation-ICD</t>
+    <t>http://example.org/ValueSet/disseminated-intravascular-coagulation-ICD</t>
   </si>
   <si>
     <t>Version</t>
